--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>Validatore di profili ICC</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>Validatore di profili ICC · realizzato con IccProfLib</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>Errore:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Converti in XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Converti in JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Converti in ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Conversione in XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Conversione in JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Conversione in ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Carica profilo ICC</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Area di rilascio per i file di profilo ICC</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ID profilo</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>rientro</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>ordina chiavi</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Avviso</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Errore</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Sconosciuto</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Attivato da</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Campo</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Valore attuale</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Richiesto: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Atteso: {value}</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>Non valido</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Chiudi</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>ordina chiavi</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Valido</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Avviso</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Errore</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Sconosciuto</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Attivato da</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Campo</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Valore attuale</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Richiesto: 0</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Atteso: {value}</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>Non valido</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Chiudi</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>rientro</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>ordina chiavi</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Output grezzo</v>
+        <v>Profile Assessment WG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Errore:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>Converti in XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>Converti in JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>Converti in ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>Conversione in XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>Conversione in JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>Conversione in ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>Carica profilo ICC</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>ID profilo</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Nome tag</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Offset</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Dimensione</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Riempimento</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Tipo</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Array di {type}</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>byte</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>Il profilo è valido</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Valido</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Avviso</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Errore</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Sconosciuto</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Attivato da</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Campo</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Valore attuale</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Richiesto: 0</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Atteso: {value}</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>Non valido</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Chiudi</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>rientro</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>ordina chiavi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Errore:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>Converti in XML</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>Converti in JSON</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>ID profilo</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Nome tag</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Offset</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Dimensione</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Riempimento</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Tipo</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Array di {type}</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>byte</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>Il profilo è valido</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Valido</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Avviso</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Errore</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Sconosciuto</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Attivato da</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Campo</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Valore attuale</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Richiesto: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Atteso: {value}</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>Non valido</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Chiudi</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>ordina chiavi</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -512,12 +512,12 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>utilizzando l’implementazione di riferimento</v>
+        <v>utilizzando l’implementazione dimostrativa</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>.</v>
@@ -525,687 +525,919 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>Convalida…</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>Salva profilo ICC</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>oppure</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Scegli file</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>File .icc e .icm</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>Intestazione</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Tag</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Convalida</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Output grezzo</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Curve</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Errore:</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>Converti in XML</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>Converti in JSON</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>Converti in ICC</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>Conversione in XML…</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>ID profilo</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Nome tag</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Offset</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Dimensione</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Riempimento</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Tipo</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Array di {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Nessun contenuto)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>byte</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Nessun output di convalida</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>Il profilo è valido</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Valido</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Avviso</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Errore</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Sconosciuto</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Attivato da</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Campo</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Valore attuale</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Richiesto: 0</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Atteso: {value}</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>Non valido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Chiudi</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>rientro</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>ordina chiavi</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>controlli</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Errore:</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>Converti in XML</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>Converti in ICC</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>Conversione in XML…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>ID profilo</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Nome tag</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Offset</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Dimensione</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Riempimento</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Tipo</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Array di {type}</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>byte</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>Il profilo è valido</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Valido</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Avviso</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Errore</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Sconosciuto</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Superato</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Non superato</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Attivato da</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Campo</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Valore attuale</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Richiesto: 0</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Atteso: {value}</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>Non valido</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Chiudi</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>rientro</v>
+        <v>ordina chiavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>ordina chiavi</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Aiuto</v>
+        <v>Formato numerico</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Contatto</v>
+        <v>Esadecimale</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Decimale</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
+        <v>Aiuto</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>utilizzando l’implementazione dimostrativa</v>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>utilizzando l’implementazione dimostrativa</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>Convalida…</v>
+        <v>.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Modificato — non salvato</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>oppure</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Scegli file</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>File .icc e .icm</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>Intestazione</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Tag</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Convalida</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Grafico</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Output grezzo</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Curve</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Curve di ingresso</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Curve di uscita</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>Immagine CLUT</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Immagine gamut</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Cromaticità</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Tabella della curva</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tabelle</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Dati</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Valuta</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>Caricamento…</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Ingresso</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Uscita</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Virgola mobile</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Punto griglia</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normalizzato</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Leggibile</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>Caricamento…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Sicurezza</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Conformità</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Qualità</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>RAPPORTO</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>NON SUPERATO</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>controlli</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Errore:</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>Converti in XML</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>Converti in JSON</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>Converti in ICC</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>ID profilo</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Nome tag</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Offset</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Dimensione</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Riempimento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Tipo</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Array di {type}</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>byte</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>Il profilo è valido</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Valido</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Avviso</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Errore</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Sconosciuto</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Superato</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Non superato</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Attivato da</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Campo</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Valore attuale</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Richiesto: 0</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Atteso: {value}</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>Non valido</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Chiudi</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>rientro</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>ordina chiavi</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Sicurezza</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Conformità</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Qualità</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>RAPPORTO</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Errore:</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Grafico</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Output grezzo</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Curve</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Curve di ingresso</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Curve di uscita</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>Immagine CLUT</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Immagine gamut</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Cromaticità</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Grafico a dispersione</v>
+        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Mostra altri ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Tabella della curva</v>
+        <v>Tutti</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tabelle</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Dati</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Valuta</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>Caricamento…</v>
+        <v>Inversione di tono L*</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Ingresso</v>
+        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Uscita</v>
+        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Virgola mobile</v>
+        <v>Tabella LUT</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Punto griglia</v>
+        <v>Soglia ΔL* (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normalizzato</v>
+        <v>{n} inversioni oltre ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Leggibile</v>
+        <v>Nessuna inversione L* oltre ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Canale</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Inchiostro (basso → alto)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>Caricamento…</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Sicurezza</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Conformità</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Qualità</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>RAPPORTO</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>NON SUPERATO</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>controlli</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Errore:</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>Converti in XML</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>Converti in JSON</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>Converti in ICC</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>Conversione in XML…</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>Carica profilo ICC</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>ID profilo</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Nome tag</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Offset</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Dimensione</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Riempimento</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Tipo</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Array di {type}</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>byte</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>Il profilo è valido</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Valido</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Avviso</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Errore</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Sconosciuto</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Superato</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Non superato</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Attivato da</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Campo</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Valore attuale</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Richiesto: 0</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Atteso: {value}</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>Non valido</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Chiudi</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>rientro</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>ordina chiavi</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Guida utente</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
+        <v>Cerca nella guida</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>utilizzando l’implementazione dimostrativa</v>
+        <v>Cerca nella guida utente</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>.</v>
+        <v>Risultato precedente</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Risultato successivo</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Chiudi la guida</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>Convalida…</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Impossibile caricare la guida utente.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Nessuno</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>oppure</v>
+        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Scegli file</v>
+        <v>utilizzando l’implementazione dimostrativa</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>File .icc e .icm</v>
+        <v>.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>Intestazione</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Tag</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Convalida</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Analisi</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Intento di rendering</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% inchiostro</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Percettivo</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Saturazione</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Mostra altri ({n})</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Tutti</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>Analisi in corso…</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Analisi</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>Inversione di tono L*</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>Tabella LUT</v>
+        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>Soglia ΔL* (ε)</v>
+        <v>Mostra altri ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} inversioni oltre ε = {eps}</v>
+        <v>Tutti</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Nessuna inversione L* oltre ε = {eps}</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Canale</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Inchiostro (basso → alto)</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Grafico</v>
+        <v>Inversione di tono L*</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Output grezzo</v>
+        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>Tabella LUT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Curve</v>
+        <v>Soglia ΔL* (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Curve di ingresso</v>
+        <v>{n} inversioni oltre ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Curve di uscita</v>
+        <v>Nessuna inversione L* oltre ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>Immagine CLUT</v>
+        <v>Canale</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Immagine gamut</v>
+        <v>Inchiostro (basso → alto)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Cromaticità</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Tabella della curva</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabelle</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Dati</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Valuta</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>Caricamento…</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Ingresso</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Uscita</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Virgola mobile</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Punto griglia</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normalizzato</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Leggibile</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>Caricamento…</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Sicurezza</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Conformità</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Qualità</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>RAPPORTO</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>NON SUPERATO</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>controlli</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>Iscriviti</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Chiudi</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>tu@esempio.com</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(opzionale)</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Annulla</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>Iscriviti</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Chiudi</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Errore:</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>Converti in XML</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>Converti in JSON</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>Converti in ICC</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>Conversione in XML…</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>ID profilo</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Nome tag</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Offset</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Dimensione</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Riempimento</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Tipo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Array di {type}</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>byte</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>Il profilo è valido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Errore di convalida critico</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Valido</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Avviso</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Errore</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Sconosciuto</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Superato</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Non superato</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Attivato da</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Campo</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Valore attuale</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Richiesto: 0</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Atteso: {value}</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>Non valido</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Chiudi</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>rientro</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>ordina chiavi</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Mostra altri ({n})</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Tutti</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>Analisi in corso…</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Analisi</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>Inversione di tono L*</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
+        <v>media</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>Tabella LUT</v>
+        <v>max</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>Soglia ΔL* (ε)</v>
+        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} inversioni oltre ε = {eps}</v>
+        <v>Mostra altri ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Nessuna inversione L* oltre ε = {eps}</v>
+        <v>Tutti</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Canale</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Inchiostro (basso → alto)</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Grafico</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Output grezzo</v>
+        <v>Inversione di tono L*</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Curve</v>
+        <v>Tabella LUT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Curve di ingresso</v>
+        <v>Soglia ΔL* (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Curve di uscita</v>
+        <v>{n} inversioni oltre ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>Immagine CLUT</v>
+        <v>Nessuna inversione L* oltre ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Immagine gamut</v>
+        <v>Canale</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Cromaticità</v>
+        <v>Inchiostro (basso → alto)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabella della curva</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tabelle</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Dati</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Valuta</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>Caricamento…</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Ingresso</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Uscita</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Virgola mobile</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Punto griglia</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normalizzato</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Leggibile</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Sicurezza</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Conformità</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Qualità</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>RAPPORTO</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>NON SUPERATO</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>controlli</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>Iscriviti</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Chiudi</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>tu@esempio.com</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(opzionale)</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Annulla</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>Iscriviti</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Chiudi</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Errore:</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>Converti in XML</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>Converti in JSON</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>Converti in ICC</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversione in XML…</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>ID profilo</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Nome tag</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Offset</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Dimensione</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Riempimento</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Tipo</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Array di {type}</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>byte</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>Il profilo è valido</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Errore di convalida critico</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Valido</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Avviso</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Errore</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Sconosciuto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Superato</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Non superato</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Attivato da</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Campo</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Valore attuale</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Richiesto: 0</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Atteso: {value}</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>Non valido</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Chiudi</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>rientro</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>ordina chiavi</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>I canali con molte inversioni mostrano solo le {shown} maggiori per ΔL*.</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Mostra altri ({n})</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Tutti</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>Analisi in corso…</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Analisi</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>Inversione di tono L*</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Aggiungere inchiostro non dovrebbe mai schiarire un colore. Ogni canale viene percorso tenendo fissi gli altri; ogni passo in cui L* aumenta viene segnalato. Algoritmo originariamente di Harold Boll.</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Nessuna CLUT dispositivo→PCS in questo profilo: l’analisi di inversione L* non si applica (ad esempio un profilo di visualizzazione matrice/TRC).</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabella LUT</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>Soglia ΔL* (ε)</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} inversioni oltre ε = {eps}</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Nessuna inversione L* oltre ε = {eps}</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Canale</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Inchiostro (basso → alto)</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Grafico</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Output grezzo</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Curve</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Curve di ingresso</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Curve di uscita</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>Immagine CLUT</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Immagine gamut</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Cromaticità</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Tabella della curva</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tabelle</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Dati</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Valuta</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>Caricamento…</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Ingresso</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Uscita</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Virgola mobile</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Punto griglia</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normalizzato</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Leggibile</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>Caricamento…</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Sicurezza</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Conformità</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Qualità</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>RAPPORTO</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>NON SUPERATO</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>controlli</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>tu@esempio.com</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(opzionale)</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Annulla</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>Iscriviti</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Chiudi</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Errore:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>Converti in XML</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>Converti in JSON</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>Converti in ICC</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>Conversione in XML…</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>Carica profilo ICC</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>ID profilo</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Nome tag</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Offset</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Dimensione</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Riempimento</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Tipo</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Array di {type}</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>byte</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>Il profilo è valido</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Avviso</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Errore</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Sconosciuto</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Superato</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Non superato</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Attivato da</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Campo</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Valore attuale</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Richiesto: 0</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Atteso: {value}</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>Non valido</v>
+        <v>ordina chiavi</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Chiudi</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Caricamento editor XML…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Caricamento editor JSON…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● modifiche XML non salvate</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● modifiche JSON non salvate</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>rientro</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>ordina chiavi</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>media</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>Analisi in corso…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Analisi</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Grafico</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Output grezzo</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Curve</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Curve di ingresso</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Curve di uscita</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Immagine CLUT</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Immagine gamut</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Cromaticità</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Tabella della curva</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabelle</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Dati</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Valuta</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>Caricamento…</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Ingresso</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Uscita</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Virgola mobile</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Punto griglia</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normalizzato</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Leggibile</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>Caricamento…</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Sicurezza</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Conformità</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Qualità</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>RAPPORTO</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Impostazioni</v>
+        <v>Andata e ritorno (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Visualizzazione</v>
+        <v>Andata e ritorno sul cubo dispositivo del profilo, come lo strumento di riferimento iccRoundTrip. L’andata e ritorno 1 è l’errore dispositivo→PCS→dispositivo (ΔE*ab); l’andata e ritorno 2 misura la stabilità del ciclo PCS. L’istogramma PRMG indica l’interoperabilità rispetto al Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Sfondo</v>
+        <v>Usa tag MPE (colore)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Lingua</v>
+        <v>Questo profilo non può eseguire l’andata e ritorno: mancano le trasformazioni dispositivo↔PCS necessarie (ad es. un profilo unidirezionale o astratto).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>Sistema</v>
+        <v>Andata e ritorno ignorata: lo spazio colore del dispositivo è troppo ampio da valutare (troppi campioni).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Chiaro</v>
+        <v>Metrica</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Scuro</v>
+        <v>Andata e ritorno 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Predefinito di sistema</v>
+        <v>Andata e ritorno 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Formato numerico</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Esadecimale</v>
+        <v>stabilità del ciclo PCS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Decimale</v>
+        <v>ΔE min</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Aiuto</v>
+        <v>ΔE medio</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Contatto</v>
+        <v>ΔE max</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Guida utente</v>
+        <v>Peggiore L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Cerca nella guida</v>
+        <v>Gamut specificato</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Cerca nella guida utente</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Risultato precedente</v>
+        <v>Non specificato</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Risultato successivo</v>
+        <v>Non valutato</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Chiudi la guida</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>Caricamento…</v>
+        <v>ΔE andata e ritorno</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>Impossibile caricare la guida utente.</v>
+        <v>Conteggio</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Nessuno</v>
+        <v>Quota</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Totale</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
+        <v>PRMG non valutato</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>utilizzando l’implementazione dimostrativa</v>
+        <v>Impostazioni</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>.</v>
+        <v>Visualizzazione</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Sfondo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Lingua</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>Convalida…</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Chiaro</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Scuro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Predefinito di sistema</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>oppure</v>
+        <v>Formato numerico</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Scegli file</v>
+        <v>Esadecimale</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>File .icc e .icm</v>
+        <v>Decimale</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>Intestazione</v>
+        <v>Aiuto</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Tag</v>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Convalida</v>
+        <v>Guida utente</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Analisi</v>
+        <v>Cerca nella guida</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Cerca nella guida utente</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Risultato precedente</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Risultato successivo</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Chiudi la guida</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Intento di rendering</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% inchiostro</v>
+        <v>Impossibile caricare la guida utente.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Percettivo</v>
+        <v>Nessuno</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Saturazione</v>
+        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>utilizzando l’implementazione dimostrativa</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Statistiche del profilo</v>
+        <v>.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Intento di rendering</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>ΔE round-trip</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>media</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>max</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>Analisi in corso…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Analisi</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Grafico</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Output grezzo</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Curve</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Curve di ingresso</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Curve di uscita</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>Immagine CLUT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Immagine gamut</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Cromaticità</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Grafico a dispersione</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Curva di risposta tonale</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabella della curva</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabelle</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Dati</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Valuta</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>Caricamento…</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Ingresso</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Uscita</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Virgola mobile</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Punto griglia</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normalizzato</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Leggibile</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>Caricamento…</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Sicurezza</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Conformità</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Qualità</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>RAPPORTO</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>NON SUPERATO</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>controlli</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>media</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>max</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>Iscriviti</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Chiudi</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>tu@esempio.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(opzionale)</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Annulla</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>Iscriviti</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Chiudi</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Errore:</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>Converti in XML</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>Converti in JSON</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>Converti in ICC</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>Conversione in XML…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversione in JSON…</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>ID profilo</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Nome tag</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Offset</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Dimensione</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Riempimento</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Tipo</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Array di {type}</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>byte</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>Il profilo è valido</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Valido</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Avviso</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Errore</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Sconosciuto</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Superato</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Non superato</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Attivato da</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Campo</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Valore attuale</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Richiesto: 0</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Atteso: {value}</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>Non valido</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Chiudi</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>rientro</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>ordina chiavi</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Impostazioni</v>
+        <v>Metriche dell’intero profilo per un intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e una metrica di accuratezza del round-trip. Scegli l’intento di rendering e il tipo di round-trip — la tabella e l’istogramma si aggiornano di conseguenza.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Visualizzazione</v>
+        <v>Tipo di round-trip</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Sfondo</v>
+        <v>Non ha effetto su questo tipo di round-trip</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Lingua</v>
+        <v>Questo tipo di round-trip non è disponibile per questo profilo.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>Sistema</v>
+        <v>Distribuzione del ΔE di round-trip</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Chiaro</v>
+        <v>Nessun campione di round-trip è rientrato nella regione valutata.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Scuro</v>
+        <v>Dev. std.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Predefinito di sistema</v>
+        <v>Frequenza relativa</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Formato numerico</v>
+        <v>Frequenza cumulativa</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Esadecimale</v>
+        <v>Scala orizzontale</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Decimale</v>
+        <v>ΔE intero</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Aiuto</v>
+        <v>Scala automatica</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Contatto</v>
+        <v>Classi</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Guida utente</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Cerca nella guida</v>
+        <v>La tabella di conversione dei colori (CLUT) di una trasformazione dispositivo↔PCS, disposta a mosaico in un’immagine. Scegli quale tabella dell’intento di rendering visualizzare.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Cerca nella guida utente</v>
+        <v>Questo profilo non ha tabelle dispositivo↔PCS basate su CLUT da visualizzare.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Risultato precedente</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Risultato successivo</v>
+        <v>La mappa dentro/fuori gamut del tag gamut: neutra dove un colore PCS è riproducibile, rossa dove cade fuori dal gamut del dispositivo.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Chiudi la guida</v>
+        <v>Questo profilo non ha un tag gamut da visualizzare.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>Caricamento…</v>
+        <v>Scala verticale</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>Impossibile caricare la guida utente.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Nessuno</v>
+        <v>Incremento tonale</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Incremento tonale (uscita − ingresso)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
+        <v>Mostra dump completo</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>utilizzando l’implementazione dimostrativa</v>
+        <v>Output troncato per prestazioni.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>.</v>
+        <v>Panoramica nel gamut (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Inversione + gamut (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Riproducibilità (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>Convalida…</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Panoramica iccviz: una griglia di valori dispositivo viene portata al PCS, di nuovo al dispositivo e ancora al PCS; il ΔE*ab è misurato tra i due passaggi PCS. Un rapido controllo di stabilità nel gamut.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab tra il PCS di ogni colore dispositivo e il suo PCS dopo un round-trip Lab → dispositivo → Lab. Riflette l’accuratezza di inversione e il gamut mapping.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab tra il primo e il secondo round-trip — quanto è stabile un round-trip PCS ripetuto (riproducibilità, indipendente dal clipping di gamut del primo passaggio).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: i colori PCS all’interno del Perceptual Reference Medium Gamut eseguono un singolo round-trip (Lab → dispositivo → Lab); la distribuzione del ΔE*ab indica l’interoperabilità tra profili.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Impostazioni</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Visualizzazione</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Sfondo</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Lingua</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Chiaro</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Scuro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Predefinito di sistema</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Formato numerico</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Esadecimale</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Decimale</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Aiuto</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Guida utente</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Cerca nella guida</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Cerca nella guida utente</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Risultato precedente</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Risultato successivo</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Chiudi la guida</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Impossibile caricare la guida utente.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Nessuno</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>oppure</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Scegli file</v>
+        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>File .icc e .icm</v>
+        <v>utilizzando l’implementazione dimostrativa</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>Intestazione</v>
+        <v>.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Tag</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Convalida</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Analisi</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Profili</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Mostra il pool di profili</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Intento di rendering</v>
+        <v>Comprimi</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% inchiostro</v>
+        <v>Carica profili</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Percettivo</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Trascina qui i profili ICC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Saturazione</v>
+        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Nuovo da .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Nuovo profilo da .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Intento di rendering</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Scegli file .cube</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>ΔE round-trip</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>oppure trascinalo qui o incolla sotto</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>media</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>max</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>Analisi in corso…</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Analisi</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Grafico</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Output grezzo</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Curve</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Curve di ingresso</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Curve di uscita</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>Immagine CLUT</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Immagine gamut</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Cromaticità</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Tabella della curva</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tabelle</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Dati</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Valuta</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Caricamento…</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Ingresso</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Uscita</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Virgola mobile</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Punto griglia</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normalizzato</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Leggibile</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Caricamento…</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Sicurezza</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Conformità</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Qualità</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>RAPPORTO</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>NON SUPERATO</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>controlli</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Iscriviti</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Chiudi</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>tu@esempio.com</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(opzionale)</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Annulla</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>Iscriviti</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Chiudi</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Errore:</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>Converti in XML</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>Converti in JSON</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>Converti in ICC</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>Conversione in XML…</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>ID profilo</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Nome tag</v>
+        <v>media</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Dimensione</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Riempimento</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Tipo</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Array di {type}</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>byte</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>Il profilo è valido</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Valido</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Avviso</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Errore</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Sconosciuto</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Superato</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Non superato</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Attivato da</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Campo</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Valore attuale</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Richiesto: 0</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Atteso: {value}</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>Non valido</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Chiudi</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>rientro</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>ordina chiavi</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Strumento per profili ICC</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Realizzato con {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Ricevi notifiche sulle nuove versioni</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Indirizzo e-mail</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>tu@esempio.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Come utilizzerai profiletool?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(opzionale)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Annulla</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Grazie — ti ricontatteremo.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Informativa sulla privacy</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Inserisci un indirizzo e-mail valido.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Troppe richieste. Riprova più tardi.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Controlla il modulo e riprova.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Impossibile inviare la richiesta. Riprova.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Errore di rete. Riprova.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Errore:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Converti in XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Converti in JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Converti in ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Conversione in XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Conversione in JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Conversione in ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Carica profilo ICC</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Area di rilascio per i file di profilo ICC</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ID profilo</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Collega</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Rimuovi</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Confronto di gamut</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Intento di rendering</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Guscio</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Wireframe</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacità</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Colore</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Pieno</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Per valore</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Per tonalità</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotazione</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbita</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Rollio</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocità di rollio</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>nessun gamut</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostra / nascondi</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Piano</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Collegamento</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>Generatore di display V4</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>Display RGB V5</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Crea profilo display V4</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Nome del profilo</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Crea</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>Creazione…</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Annulla</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} file non caricati</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>oppure</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Scegli file</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>File .icc e .icm</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>Intestazione</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Tag</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Convalida</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Analisi</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Intento di rendering</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% inchiostro</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Percettivo</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Saturazione</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Intento di rendering</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>ΔE round-trip</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>media</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>max</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>Analisi in corso…</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Analisi</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Grafico</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Output grezzo</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Curve</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Curve di ingresso</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Curve di uscita</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>Immagine CLUT</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Immagine gamut</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Cromaticità</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Tabella della curva</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tabelle</v>
+        <v>media</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Dati</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Valuta</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>Caricamento…</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Ingresso</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Uscita</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Virgola mobile</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Punto griglia</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normalizzato</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Leggibile</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>Caricamento…</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Sicurezza</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Conformità</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Qualità</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>RAPPORTO</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>NON SUPERATO</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>controlli</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>Iscriviti</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Chiudi</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>tu@esempio.com</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(opzionale)</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>can</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Annulla</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>Iscriviti</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Chiudi</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Errore:</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>Converti in XML</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>Converti in JSON</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>Converti in ICC</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>Conversione in XML…</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>Carica profilo ICC</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>ID profilo</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Nome tag</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Offset</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Dimensione</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Riempimento</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Tipo</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Array di {type}</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>byte</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>media</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>Il profilo è valido</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Valido</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Avviso</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Errore</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Sconosciuto</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Superato</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Non superato</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Attivato da</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Campo</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Valore attuale</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Richiesto: 0</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Atteso: {value}</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>Non valido</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Chiudi</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>rientro</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>ordina chiavi</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Rapporto Profile Assessment WG</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Sicurezza</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Conformità</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Qualità</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>RAPPORTO</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>NON SUPERATO</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>controlli</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Strumento per profili ICC</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Realizzato con {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Ricevi notifiche sulle nuove versioni</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Indirizzo e-mail</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>tu@esempio.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Come utilizzerai profiletool?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(opzionale)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Annulla</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Iscriviti</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Grazie — ti ricontatteremo.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Informativa sulla privacy</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Inserisci un indirizzo e-mail valido.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Troppe richieste. Riprova più tardi.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Controlla il modulo e riprova.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Impossibile inviare la richiesta. Riprova.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Errore di rete. Riprova.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Errore:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Converti in XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Converti in JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Converti in ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Conversione in XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Conversione in JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Conversione in ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Carica profilo ICC</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Area di rilascio per i file di profilo ICC</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>ID profilo</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Carica un profilo ICC per convalidarlo rispetto alla specifica</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>utilizzando l’implementazione dimostrativa</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>.</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>Convalida…</v>
+        <v>Profili</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Mostra il pool di profili</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Comprimi</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Profili</v>
+        <v>Carica profili</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Mostra il pool di profili</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Comprimi</v>
+        <v>Trascina qui i profili ICC</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Carica profili</v>
+        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Rimuovi</v>
+        <v>Nuovo da .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>Trascina qui i profili ICC</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Nuovo da .cube</v>
+        <v>Nuovo profilo da .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Ordina per nome</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>Scegli file .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Nuovo profilo da .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Scegli file .cube</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>oppure trascinalo qui o incolla sotto</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Annulla</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Crea DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Creazione…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Annulla</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>Creazione…</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>Impossibile leggere questo file.</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Profilo</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Confronta</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Collega</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Spettrale</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Rimuovi</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Confronto di gamut</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Intento di rendering</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Guscio</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Wireframe</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Numeri degli assi</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Opacità</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Colore</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Pieno</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Per valore</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Per tonalità</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotazione</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Orbita</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Rollio</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocità di rollio</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>nessun gamut</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Mostra / nascondi</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Piano</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Collegamento</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>Generatore di display V4</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>Display RGB V5</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>Crea profilo display V4</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Nome del profilo</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Crea</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>Creazione…</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Pipeline di collegamento</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Fatto</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>Controllo immagine…</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Trasforma immagine</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>Trasformazione…</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Trascina i profili per avviare la catena</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>rimosso</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Sposta prima</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Sposta dopo</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Sposta su</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Sposta giù</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Intento di rendering (tutti)</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Intento di rendering per questa trasformazione</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>Le trasformazioni usano intenti di rendering diversi</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Catena</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Non è stato possibile analizzare la catena.</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>Controllo della catena…</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>La catena non si collega ({detail}).</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Correggi la catena prima di elaborare le immagini</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Svuota</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>Nome del DeviceLink</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>Creazione…</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Crea una catena per elaborare le immagini</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Immagine trasformata salvata.</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>Impossibile leggere il file.</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>File di dati troppo grande.</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Trasforma dati</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>Trasformazione…</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Preferisci</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Osservatore</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Illuminante</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Condizione</v>
+        <v>media</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>Filtra {n} duplicato/i</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>mediana</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>media</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>patch</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} duplicati</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Risultato della trasformazione</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} patch</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Salva con nome</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Salva</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverti trasformazione</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>Inversione…</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverti</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>ultima fase</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>prima fase</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Dati in {in} → ricerca {out}</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>L'inversione richiede una catena di 2–3 profili</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>Costo ΔE</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Questa immagine contiene un profilo ICC incorporato.</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Estrai e aggiungi alla catena</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>Estrazione…</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Ignora</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Opzioni di output dell'immagine</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Codifica</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Come l'origine</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 bit</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 bit</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Virgola mobile (32 bit)</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Compressione</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Nessuna</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planare</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Interlacciato</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Separato</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>Interpolazione CMM</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tetraedrica</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Lineare</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>Incorpora profilo ICC</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Assembla TIFF spettrale</v>
+        <v>can</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>can</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Assembla e salva</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>Assemblaggio…</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>Assemblati {n} canali.</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Annulla</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} file non caricati</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>oppure</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Scegli file</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>File .icc e .icm</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>Intestazione</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Tag</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Convalida</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Analisi</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Intento di rendering</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% inchiostro</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Percettivo</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Saturazione</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Intento di rendering</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>media</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>ΔE round-trip</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>media</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>max</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>Analisi in corso…</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Analisi</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Grafico</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Output grezzo</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Curve</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Curve di ingresso</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Curve di uscita</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>Immagine CLUT</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Immagine gamut</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Cromaticità</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Tabella della curva</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tabelle</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Dati</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Valuta</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>Caricamento…</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Ingresso</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Uscita</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Virgola mobile</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Punto griglia</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normalizzato</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Leggibile</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>Caricamento…</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Sicurezza</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Conformità</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Qualità</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>RAPPORTO</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>NON SUPERATO</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>controlli</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>Iscriviti</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Chiudi</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>tu@esempio.com</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(opzionale)</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Annulla</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>Iscriviti</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Chiudi</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Errore:</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>Converti in XML</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>Converti in JSON</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>Converti in ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>Conversione in XML…</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>Conversione in ICC…</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>ID profilo</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Nome tag</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Offset</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Dimensione</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Riempimento</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Tipo</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Array di {type}</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>byte</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>Il profilo è valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Valido</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Avviso</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Errore</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Sconosciuto</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Superato</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Non superato</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Attivato da</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Campo</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Valore attuale</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Richiesto: 0</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Atteso: {value}</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>Non valido</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Chiudi</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>ordina chiavi</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>rientro</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>ordina chiavi</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Andata e ritorno (PRMG)</v>
+        <v>Il {pct}% dei campioni era fuori intervallo ed è stato limitato.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Andata e ritorno sul cubo dispositivo del profilo, come lo strumento di riferimento iccRoundTrip. L’andata e ritorno 1 è l’errore dispositivo→PCS→dispositivo (ΔE*ab); l’andata e ritorno 2 misura la stabilità del ciclo PCS. L’istogramma PRMG indica l’interoperabilità rispetto al Perceptual Reference Medium Gamut.</v>
+        <v>Andata e ritorno (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>Usa tag MPE (colore)</v>
+        <v>Andata e ritorno sul cubo dispositivo del profilo, come lo strumento di riferimento iccRoundTrip. L’andata e ritorno 1 è l’errore dispositivo→PCS→dispositivo (ΔE*ab); l’andata e ritorno 2 misura la stabilità del ciclo PCS. L’istogramma PRMG indica l’interoperabilità rispetto al Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Questo profilo non può eseguire l’andata e ritorno: mancano le trasformazioni dispositivo↔PCS necessarie (ad es. un profilo unidirezionale o astratto).</v>
+        <v>Usa tag MPE (colore)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Andata e ritorno ignorata: lo spazio colore del dispositivo è troppo ampio da valutare (troppi campioni).</v>
+        <v>Questo profilo non può eseguire l’andata e ritorno: mancano le trasformazioni dispositivo↔PCS necessarie (ad es. un profilo unidirezionale o astratto).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Metrica</v>
+        <v>Andata e ritorno ignorata: lo spazio colore del dispositivo è troppo ampio da valutare (troppi campioni).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Andata e ritorno 1</v>
+        <v>Metrica</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Andata e ritorno 2</v>
+        <v>Andata e ritorno 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>dispositivo → PCS → dispositivo</v>
+        <v>Andata e ritorno 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>stabilità del ciclo PCS</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>ΔE min</v>
+        <v>stabilità del ciclo PCS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>ΔE medio</v>
+        <v>ΔE min</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>ΔE max</v>
+        <v>ΔE medio</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Peggiore L, a, b</v>
+        <v>ΔE max</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Gamut specificato</v>
+        <v>Peggiore L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Gamut specificato</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>Non specificato</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>Non valutato</v>
+        <v>Non specificato</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>Interoperabilità PRMG</v>
+        <v>Non valutato</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>ΔE andata e ritorno</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Conteggio</v>
+        <v>ΔE andata e ritorno</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Quota</v>
+        <v>Conteggio</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Totale</v>
+        <v>Quota</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG non valutato</v>
+        <v>Totale</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Metriche dell’intero profilo per un intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e una metrica di accuratezza del round-trip. Scegli l’intento di rendering e il tipo di round-trip — la tabella e l’istogramma si aggiornano di conseguenza.</v>
+        <v>PRMG non valutato</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Tipo di round-trip</v>
+        <v>Metriche dell’intero profilo per un intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e una metrica di accuratezza del round-trip. Scegli l’intento di rendering e il tipo di round-trip — la tabella e l’istogramma si aggiornano di conseguenza.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Non ha effetto su questo tipo di round-trip</v>
+        <v>Tipo di round-trip</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Questo tipo di round-trip non è disponibile per questo profilo.</v>
+        <v>Non ha effetto su questo tipo di round-trip</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Distribuzione del ΔE di round-trip</v>
+        <v>Questo tipo di round-trip non è disponibile per questo profilo.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Nessun campione di round-trip è rientrato nella regione valutata.</v>
+        <v>Distribuzione del ΔE di round-trip</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Dev. std.</v>
+        <v>Nessun campione di round-trip è rientrato nella regione valutata.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Frequenza relativa</v>
+        <v>Dev. std.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Frequenza cumulativa</v>
+        <v>Frequenza relativa</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Scala orizzontale</v>
+        <v>Frequenza cumulativa</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>ΔE intero</v>
+        <v>Scala orizzontale</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Scala automatica</v>
+        <v>ΔE intero</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Classi</v>
+        <v>Scala automatica</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>Immagine CLUT</v>
+        <v>Classi</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>La tabella di conversione dei colori (CLUT) di una trasformazione dispositivo↔PCS, disposta a mosaico in un’immagine. Scegli quale tabella dell’intento di rendering visualizzare.</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Questo profilo non ha tabelle dispositivo↔PCS basate su CLUT da visualizzare.</v>
+        <v>La tabella di conversione dei colori (CLUT) di una trasformazione dispositivo↔PCS, disposta a mosaico in un’immagine. Scegli quale tabella dell’intento di rendering visualizzare.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Immagine gamut</v>
+        <v>Questo profilo non ha tabelle dispositivo↔PCS basate su CLUT da visualizzare.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>La mappa dentro/fuori gamut del tag gamut: neutra dove un colore PCS è riproducibile, rossa dove cade fuori dal gamut del dispositivo.</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Questo profilo non ha un tag gamut da visualizzare.</v>
+        <v>La mappa dentro/fuori gamut del tag gamut: neutra dove un colore PCS è riproducibile, rossa dove cade fuori dal gamut del dispositivo.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Scala verticale</v>
+        <v>Questo profilo non ha un tag gamut da visualizzare.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Scala verticale</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Incremento tonale</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Incremento tonale (uscita − ingresso)</v>
+        <v>Incremento tonale</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Mostra dump completo</v>
+        <v>Incremento tonale (uscita − ingresso)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Output troncato per prestazioni.</v>
+        <v>Mostra dump completo</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>Panoramica nel gamut (RT0)</v>
+        <v>Output troncato per prestazioni.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversione + gamut (RT1)</v>
+        <v>Panoramica nel gamut (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Riproducibilità (RT2)</v>
+        <v>Inversione + gamut (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>Interoperabilità PRMG</v>
+        <v>Riproducibilità (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>Panoramica iccviz: una griglia di valori dispositivo viene portata al PCS, di nuovo al dispositivo e ancora al PCS; il ΔE*ab è misurato tra i due passaggi PCS. Un rapido controllo di stabilità nel gamut.</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab tra il PCS di ogni colore dispositivo e il suo PCS dopo un round-trip Lab → dispositivo → Lab. Riflette l’accuratezza di inversione e il gamut mapping.</v>
+        <v>Panoramica iccviz: una griglia di valori dispositivo viene portata al PCS, di nuovo al dispositivo e ancora al PCS; il ΔE*ab è misurato tra i due passaggi PCS. Un rapido controllo di stabilità nel gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab tra il primo e il secondo round-trip — quanto è stabile un round-trip PCS ripetuto (riproducibilità, indipendente dal clipping di gamut del primo passaggio).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab tra il PCS di ogni colore dispositivo e il suo PCS dopo un round-trip Lab → dispositivo → Lab. Riflette l’accuratezza di inversione e il gamut mapping.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: i colori PCS all’interno del Perceptual Reference Medium Gamut eseguono un singolo round-trip (Lab → dispositivo → Lab); la distribuzione del ΔE*ab indica l’interoperabilità tra profili.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab tra il primo e il secondo round-trip — quanto è stabile un round-trip PCS ripetuto (riproducibilità, indipendente dal clipping di gamut del primo passaggio).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Impostazioni</v>
+        <v>iccRoundTrip PRMG: i colori PCS all’interno del Perceptual Reference Medium Gamut eseguono un singolo round-trip (Lab → dispositivo → Lab); la distribuzione del ΔE*ab indica l’interoperabilità tra profili.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Visualizzazione</v>
+        <v>Impostazioni</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Sfondo</v>
+        <v>Visualizzazione</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Lingua</v>
+        <v>Sfondo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>Sistema</v>
+        <v>Lingua</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Chiaro</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Scuro</v>
+        <v>Chiaro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Predefinito di sistema</v>
+        <v>Scuro</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Formato numerico</v>
+        <v>Predefinito di sistema</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Esadecimale</v>
+        <v>Formato numerico</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Decimale</v>
+        <v>Esadecimale</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Aiuto</v>
+        <v>Decimale</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Contatto</v>
+        <v>Aiuto</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Guida utente</v>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Cerca nella guida</v>
+        <v>Guida utente</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Cerca nella guida utente</v>
+        <v>Cerca nella guida</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Risultato precedente</v>
+        <v>Cerca nella guida utente</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Risultato successivo</v>
+        <v>Risultato precedente</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Chiudi la guida</v>
+        <v>Risultato successivo</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Caricamento…</v>
+        <v>Chiudi la guida</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Impossibile caricare la guida utente.</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Nessuno</v>
+        <v>Impossibile caricare la guida utente.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Nessuno</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>Convalida…</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Profili</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Mostra il pool di profili</v>
+        <v>Profili</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Comprimi</v>
+        <v>Mostra il pool di profili</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Carica profili</v>
+        <v>Comprimi</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Rimuovi</v>
+        <v>Carica profili</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>Trascina qui i profili ICC</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
+        <v>Trascina qui i profili ICC</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Nuovo da .cube</v>
+        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Ordina per nome</v>
+        <v>Nuovo da .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Nuovo profilo da .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
+        <v>Nuovo profilo da .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>Scegli file .cube</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Scegli file .cube</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>oppure trascinalo qui o incolla sotto</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Annulla</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>Creazione…</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>Impossibile leggere questo file.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Profilo</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Confronta</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Collega</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Spettrale</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Rimuovi</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Confronto di gamut</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Intento di rendering</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Guscio</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Wireframe</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Numeri degli assi</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Opacità</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Colore</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Pieno</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Per valore</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Per tonalità</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotazione</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Orbita</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Rollio</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Velocità di rollio</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>nessun gamut</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Mostra / nascondi</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Piano</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Collegamento</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Generatore di display V4</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>Display RGB V5</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Crea profilo display V4</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Nome del profilo</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Crea</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Creazione…</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Pipeline di collegamento</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Fatto</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>Controllo immagine…</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Trasforma immagine</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Trascina i profili per avviare la catena</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>rimosso</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Sposta prima</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Sposta dopo</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Sposta su</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Sposta giù</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Intento di rendering (tutti)</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Intento di rendering per questa trasformazione</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>Le trasformazioni usano intenti di rendering diversi</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Catena</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>Non è stato possibile analizzare la catena.</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>Controllo della catena…</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>La catena non si collega ({detail}).</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Correggi la catena prima di elaborare le immagini</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Svuota</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>Nome del DeviceLink</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>Creazione…</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Crea una catena per elaborare le immagini</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Immagine trasformata salvata.</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>Impossibile leggere il file.</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>File di dati troppo grande.</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Trasforma dati</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Preferisci</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Osservatore</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Illuminante</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Condizione</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>Filtra {n} duplicato/i</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>mediana</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>patch</v>
+        <v>media</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} duplicati</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Risultato della trasformazione</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} patch</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Salva con nome</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Salva</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Inverti trasformazione</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>Inversione…</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Inverti</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>ultima fase</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>prima fase</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Dati in {in} → ricerca {out}</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>L'inversione richiede una catena di 2–3 profili</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>Costo ΔE</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Questa immagine contiene un profilo ICC incorporato.</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Estrai e aggiungi alla catena</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Estrazione…</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Ignora</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Opzioni di output dell'immagine</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Codifica</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Come l'origine</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 bit</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 bit</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Virgola mobile (32 bit)</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Compressione</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Nessuna</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planare</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Interlacciato</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Separato</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>Interpolazione CMM</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tetraedrica</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Lineare</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>Incorpora profilo ICC</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Assembla TIFF spettrale</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>can</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Assembla e salva</v>
+        <v>can</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>Assemblaggio…</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>Assemblati {n} canali.</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Annulla</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} file non caricati</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>oppure</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Scegli file</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>File .icc e .icm</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>Intestazione</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Tag</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Convalida</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Analisi</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Intento di rendering</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% inchiostro</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Percettivo</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Saturazione</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Intento di rendering</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>ΔE round-trip</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>media</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>Analisi in corso…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Analisi</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Grafico</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Output grezzo</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Curve</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Curve di ingresso</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Curve di uscita</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Immagine CLUT</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Immagine gamut</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Cromaticità</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Tabella della curva</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabelle</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Dati</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Valuta</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>Caricamento…</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Ingresso</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Uscita</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Virgola mobile</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Punto griglia</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normalizzato</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Leggibile</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>Caricamento…</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Sicurezza</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Conformità</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Qualità</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>RAPPORTO</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Percettivo</v>
+        <v>L* in uscita (tono)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Saturazione</v>
+        <v>Colorimetria degli estremi</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Assoluta</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Intento di rendering</v>
+        <v>Punto di bianco</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Punto di nero</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>ΔE round-trip</v>
+        <v>Inchiostrazione al punto di nero</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>media</v>
+        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>max</v>
+        <v>Pieno e croma massima</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>Analisi in corso…</v>
+        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Analisi</v>
+        <v>Tinta</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Grafico</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Output grezzo</v>
+        <v>All’inchiostrazione</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Uso dell’inchiostro nelle ombre</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Curve</v>
+        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Curve di ingresso</v>
+        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Curve di uscita</v>
+        <v>Piano a L* costante</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>Immagine CLUT</v>
+        <v>con compensazione del punto di nero da</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Immagine gamut</v>
+        <v>Posizione lungo il percorso</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Cromaticità</v>
+        <v>Percorso</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabella della curva</v>
+        <v>Giallo</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tabelle</v>
+        <v>Rosso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Dati</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Valuta</v>
+        <v>Blu</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>Caricamento…</v>
+        <v>Nero</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Ingresso</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Uscita</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Virgola mobile</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Punto griglia</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normalizzato</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Leggibile</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>Caricamento…</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>media</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>max</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Sicurezza</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Conformità</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Qualità</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>RAPPORTO</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>NON SUPERATO</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>controlli</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>Iscriviti</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Chiudi</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>tu@esempio.com</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(opzionale)</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Annulla</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>Iscriviti</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Chiudi</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Errore:</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>Converti in XML</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>Converti in JSON</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>Converti in ICC</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>Conversione in XML…</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>Conversione in JSON…</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>Conversione in ICC…</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>Carica profilo ICC</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>ID profilo</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Nome tag</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Offset</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Dimensione</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Riempimento</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Tipo</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Array di {type}</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>byte</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>Il profilo è valido</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Valido</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Avviso</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Errore</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Sconosciuto</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Superato</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Non superato</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Attivato da</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Campo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Valore attuale</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Richiesto: 0</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Atteso: {value}</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>Non valido</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Chiudi</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>rientro</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>ordina chiavi</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Gamut specificato</v>
+        <v>ΔE di andata e ritorno per luminosità</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (luminosità del colore richiesto)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>Non specificato</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>Non valutato</v>
+        <v>punti, confine del gamut → neutro</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>Interoperabilità PRMG</v>
+        <v>Gamut specificato</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>ΔE andata e ritorno</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Conteggio</v>
+        <v>Non specificato</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Quota</v>
+        <v>Non valutato</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Totale</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG non valutato</v>
+        <v>ΔE andata e ritorno</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Metriche dell’intero profilo per un intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e una metrica di accuratezza del round-trip. Scegli l’intento di rendering e il tipo di round-trip — la tabella e l’istogramma si aggiornano di conseguenza.</v>
+        <v>Conteggio</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Tipo di round-trip</v>
+        <v>Quota</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>Non ha effetto su questo tipo di round-trip</v>
+        <v>Totale</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Questo tipo di round-trip non è disponibile per questo profilo.</v>
+        <v>PRMG non valutato</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Distribuzione del ΔE di round-trip</v>
+        <v>Metriche dell’intero profilo per un intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e una metrica di accuratezza del round-trip. Scegli l’intento di rendering e il tipo di round-trip — la tabella e l’istogramma si aggiornano di conseguenza.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Nessun campione di round-trip è rientrato nella regione valutata.</v>
+        <v>Tipo di round-trip</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Dev. std.</v>
+        <v>Non ha effetto su questo tipo di round-trip</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Frequenza relativa</v>
+        <v>Questo tipo di round-trip non è disponibile per questo profilo.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Frequenza cumulativa</v>
+        <v>Distribuzione del ΔE di round-trip</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Scala orizzontale</v>
+        <v>Nessun campione di round-trip è rientrato nella regione valutata.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>ΔE intero</v>
+        <v>Dev. std.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Scala automatica</v>
+        <v>Frequenza relativa</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Classi</v>
+        <v>Frequenza cumulativa</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>Immagine CLUT</v>
+        <v>Scala orizzontale</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>La tabella di conversione dei colori (CLUT) di una trasformazione dispositivo↔PCS, disposta a mosaico in un’immagine. Scegli quale tabella dell’intento di rendering visualizzare.</v>
+        <v>ΔE intero</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Questo profilo non ha tabelle dispositivo↔PCS basate su CLUT da visualizzare.</v>
+        <v>Scala automatica</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Immagine gamut</v>
+        <v>Classi</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>La mappa dentro/fuori gamut del tag gamut: neutra dove un colore PCS è riproducibile, rossa dove cade fuori dal gamut del dispositivo.</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Questo profilo non ha un tag gamut da visualizzare.</v>
+        <v>La tabella di conversione dei colori (CLUT) di una trasformazione dispositivo↔PCS, disposta a mosaico in un’immagine. Scegli quale tabella dell’intento di rendering visualizzare.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Scala verticale</v>
+        <v>Questo profilo non ha tabelle dispositivo↔PCS basate su CLUT da visualizzare.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Incremento tonale</v>
+        <v>La mappa dentro/fuori gamut del tag gamut: neutra dove un colore PCS è riproducibile, rossa dove cade fuori dal gamut del dispositivo.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Incremento tonale (uscita − ingresso)</v>
+        <v>Questo profilo non ha un tag gamut da visualizzare.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Mostra dump completo</v>
+        <v>Scala verticale</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Output troncato per prestazioni.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>Panoramica nel gamut (RT0)</v>
+        <v>Incremento tonale</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversione + gamut (RT1)</v>
+        <v>Incremento tonale (uscita − ingresso)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Riproducibilità (RT2)</v>
+        <v>Mostra dump completo</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>Interoperabilità PRMG</v>
+        <v>Output troncato per prestazioni.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>Panoramica iccviz: una griglia di valori dispositivo viene portata al PCS, di nuovo al dispositivo e ancora al PCS; il ΔE*ab è misurato tra i due passaggi PCS. Un rapido controllo di stabilità nel gamut.</v>
+        <v>Panoramica nel gamut (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab tra il PCS di ogni colore dispositivo e il suo PCS dopo un round-trip Lab → dispositivo → Lab. Riflette l’accuratezza di inversione e il gamut mapping.</v>
+        <v>Inversione + gamut (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab tra il primo e il secondo round-trip — quanto è stabile un round-trip PCS ripetuto (riproducibilità, indipendente dal clipping di gamut del primo passaggio).</v>
+        <v>Riproducibilità (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: i colori PCS all’interno del Perceptual Reference Medium Gamut eseguono un singolo round-trip (Lab → dispositivo → Lab); la distribuzione del ΔE*ab indica l’interoperabilità tra profili.</v>
+        <v>Interoperabilità PRMG</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Impostazioni</v>
+        <v>Panoramica iccviz: una griglia di valori dispositivo viene portata al PCS, di nuovo al dispositivo e ancora al PCS; il ΔE*ab è misurato tra i due passaggi PCS. Un rapido controllo di stabilità nel gamut.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Visualizzazione</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab tra il PCS di ogni colore dispositivo e il suo PCS dopo un round-trip Lab → dispositivo → Lab. Riflette l’accuratezza di inversione e il gamut mapping.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Sfondo</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab tra il primo e il secondo round-trip — quanto è stabile un round-trip PCS ripetuto (riproducibilità, indipendente dal clipping di gamut del primo passaggio).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Lingua</v>
+        <v>iccRoundTrip PRMG: i colori PCS all’interno del Perceptual Reference Medium Gamut eseguono un singolo round-trip (Lab → dispositivo → Lab); la distribuzione del ΔE*ab indica l’interoperabilità tra profili.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>Sistema</v>
+        <v>Impostazioni</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Chiaro</v>
+        <v>Visualizzazione</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Scuro</v>
+        <v>Sfondo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Predefinito di sistema</v>
+        <v>Lingua</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Formato numerico</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Esadecimale</v>
+        <v>Chiaro</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Decimale</v>
+        <v>Scuro</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Aiuto</v>
+        <v>Predefinito di sistema</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Contatto</v>
+        <v>Formato numerico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Guida utente</v>
+        <v>Esadecimale</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Cerca nella guida</v>
+        <v>Decimale</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Cerca nella guida utente</v>
+        <v>Aiuto</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Risultato precedente</v>
+        <v>Contatto</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Risultato successivo</v>
+        <v>Guida utente</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Chiudi la guida</v>
+        <v>Cerca nella guida</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>Caricamento…</v>
+        <v>Cerca nella guida utente</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>Impossibile caricare la guida utente.</v>
+        <v>Risultato precedente</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Nessuno</v>
+        <v>Risultato successivo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Chiudi la guida</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Basato sull’implementazione dimostrativa di</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Impossibile caricare la guida utente.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>Convalida…</v>
+        <v>Nessuno</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>Salva profilo ICC</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Modificato — non salvato</v>
+        <v>Basato sull’implementazione dimostrativa di</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Profili</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Mostra il pool di profili</v>
+        <v>Convalida…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Comprimi</v>
+        <v>Salva profilo ICC</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Carica profili</v>
+        <v>● Modificato — non salvato</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Rimuovi</v>
+        <v>Profili</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>Trascina qui i profili ICC</v>
+        <v>Mostra il pool di profili</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
+        <v>Comprimi</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Nuovo da .cube</v>
+        <v>Carica profili</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Ordina per nome</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>Trascina qui i profili ICC</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Nuovo profilo da .cube</v>
+        <v>o un’immagine (TIFF/PNG/JPEG) per estrarne il profilo incorporato — i file restano sul tuo dispositivo.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
+        <v>Nuovo da .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>Scegli file .cube</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Nuovo profilo da .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Scegli file .cube</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>oppure trascinalo qui o incolla sotto</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Annulla</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Crea DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Creazione…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Impossibile leggere questo file.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Profilo</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Confronta</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Collega</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Spettrale</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Rimuovi</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Confronto di gamut</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Intento di rendering</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Guscio</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Wireframe</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Numeri degli assi</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacità</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Colore</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Pieno</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Per valore</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Per tonalità</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotazione</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbita</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Rollio</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocità di rollio</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>nessun gamut</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostra / nascondi</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Piano</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Collegamento</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>Generatore di display V4</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>Display RGB V5</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Crea profilo display V4</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Nome del profilo</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Crea</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>Creazione…</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Pipeline di collegamento</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Fatto</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>Controllo immagine…</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Trasforma immagine</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>Trasformazione…</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Trascina i profili per avviare la catena</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>rimosso</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Sposta prima</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Sposta dopo</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Sposta su</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Sposta giù</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Intento di rendering (tutti)</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Intento di rendering per questa trasformazione</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>Le trasformazioni usano intenti di rendering diversi</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Catena</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>Non è stato possibile analizzare la catena.</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>Controllo della catena…</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>La catena non si collega ({detail}).</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Correggi la catena prima di elaborare le immagini</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Svuota</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>Crea DeviceLink</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Nome del DeviceLink</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>Creazione…</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Crea una catena per elaborare le immagini</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Immagine trasformata salvata.</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>Impossibile leggere il file.</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>File di dati troppo grande.</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Trasforma dati</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>Trasformazione…</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Preferisci</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Osservatore</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Illuminante</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Condizione</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>Filtra {n} duplicato/i</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>mediana</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>media</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>patch</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} duplicati</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Risultato della trasformazione</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} patch</v>
+        <v>media</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Salva con nome</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Salva</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Inverti trasformazione</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>Inversione…</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverti</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>ultima fase</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>prima fase</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Dati in {in} → ricerca {out}</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>L'inversione richiede una catena di 2–3 profili</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>Costo ΔE</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Questa immagine contiene un profilo ICC incorporato.</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Estrai e aggiungi alla catena</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>Estrazione…</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Ignora</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Opzioni di output dell'immagine</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Codifica</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Come l'origine</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 bit</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 bit</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Virgola mobile (32 bit)</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Compressione</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Nessuna</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planare</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Interlacciato</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Separato</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>Interpolazione CMM</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tetraedrica</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Lineare</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>Incorpora profilo ICC</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Assembla TIFF spettrale</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>can</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembla e salva</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>Assemblaggio…</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>Assemblati {n} canali.</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
+        <v>can</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Annulla</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} file non caricati</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>oppure</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Scegli file</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>File .icc e .icm</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>Intestazione</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Tag</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Convalida</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Analisi</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Intento di rendering</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% inchiostro</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* in uscita (tono)</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimetria degli estremi</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
+        <v>L* in uscita (tono)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relativa</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Assoluta</v>
+        <v>Colorimetria degli estremi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Punto di bianco</v>
+        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Punto di nero</v>
+        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Inchiostrazione al punto di nero</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Assoluta</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
+        <v>Punto di bianco</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
+        <v>Punto di nero</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Pieno e croma massima</v>
+        <v>Inchiostrazione al punto di nero</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Tinta</v>
+        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Pieno</v>
+        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>C* max</v>
+        <v>Pieno e croma massima</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>All’inchiostrazione</v>
+        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
+        <v>Tinta</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Uso dell’inchiostro nelle ombre</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
+        <v>All’inchiostrazione</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Piano a L* costante</v>
+        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>con compensazione del punto di nero da</v>
+        <v>Uso dell’inchiostro nelle ombre</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Posizione lungo il percorso</v>
+        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Percorso</v>
+        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Ciano</v>
+        <v>Piano a L* costante</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>con compensazione del punto di nero da</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Giallo</v>
+        <v>Posizione lungo il percorso</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Rosso</v>
+        <v>Percorso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Verde</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Blu</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Nero</v>
+        <v>Giallo</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Percettivo</v>
+        <v>Rosso</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Saturazione</v>
+        <v>Blu</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Nero</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Intento di rendering</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>ΔE round-trip</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>media</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>max</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>Analisi in corso…</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Analisi</v>
+        <v>media</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Grafico</v>
+        <v>max</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Output grezzo</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Curve</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Curve di ingresso</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Curve di uscita</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>Immagine CLUT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Immagine gamut</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Cromaticità</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Tabella della curva</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tabelle</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Dati</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Valuta</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>Caricamento…</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Ingresso</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Uscita</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Virgola mobile</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Punto griglia</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normalizzato</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Leggibile</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>Caricamento…</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Sicurezza</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Conformità</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Qualità</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>RAPPORTO</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>NON SUPERATO</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>controlli</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>Iscriviti</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Chiudi</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(opzionale)</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Annulla</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>Iscriviti</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Chiudi</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Errore:</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>Converti in XML</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>Converti in JSON</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>Converti in ICC</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>Conversione in XML…</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>ID profilo</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Nome tag</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Offset</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Dimensione</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Riempimento</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Tipo</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Array di {type}</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>byte</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>Il profilo è valido</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Avviso</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Errore</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Sconosciuto</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Superato</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Non superato</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Attivato da</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Campo</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Valore attuale</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Richiesto: 0</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Atteso: {value}</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>Non valido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Chiudi</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>rientro</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>ordina chiavi</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Ciano</v>
+        <v>Percorsi d’inchiostrazione primaria attraverso il neutro</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Tre percorsi nel gamut — ciano→rosso, magenta→verde, giallo→blu — ciascuno attraverso l’asse neutro alla chiarezza mediana dei suoi estremi, attraverso la tabella B2A selezionata. Ogni campione è nel gamut, quindi a differenza dei percorsi in ombra qualsiasi salto o inversione di un colorante è un difetto di regolarità della CLUT e non un artefatto di mappatura del gamut.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Giallo</v>
+        <v>I percorsi d’inchiostrazione primaria sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Rosso</v>
+        <v>Posizione lungo il percorso (neutro al centro)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Verde</v>
+        <v>Compensazione del punto nero applicata per questo intento.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Blu</v>
+        <v>Statistiche di utilizzo dell’inchiostro</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Nero</v>
+        <v>Quanto di ogni colorante il profilo deposita, come somma e come quota del totale — la firma di consumo d’inchiostro della separazione.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Percettivo</v>
+        <v>Le statistiche di utilizzo dell’inchiostro sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Asse neutro</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Saturazione</v>
+        <v>Copertura media</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Quota d’inchiostro</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Statistiche del profilo</v>
+        <v>La quota d’inchiostro è l’impronta della costruzione del neutro — la frazione di ogni colorante sul totale d’inchiostro depositato, indipendentemente dal numero di campioni.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Punti nel gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>L’utilizzo d’inchiostro su tutti i colori nel gamut richiede il confine del gamut lato B2A, non ancora implementato — in arrivo.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Intento di rendering</v>
+        <v>Nessun dato di colorante da riepilogare.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Seleziona una tabella B2A (PCS→dispositivo) qui sotto per visualizzare anche un’immagine in scala di grigi della copertura d’inchiostro per ogni colorante.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>ΔE round-trip</v>
+        <v>Copertura d’inchiostro di ogni colorante sullo stesso reticolo (più scuro = più inchiostro).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>media</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Giallo</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>max</v>
+        <v>Rosso</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>Analisi in corso…</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Analisi</v>
+        <v>Blu</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Nero</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Grafico</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Output grezzo</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Curve</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Curve di ingresso</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Curve di uscita</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>Immagine CLUT</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Immagine gamut</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Cromaticità</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>media</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Tabella della curva</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tabelle</v>
+        <v>max</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Dati</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Valuta</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>Caricamento…</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Ingresso</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Uscita</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Virgola mobile</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Punto griglia</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normalizzato</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Leggibile</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>Caricamento…</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Sicurezza</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Conformità</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Qualità</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>RAPPORTO</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>NON SUPERATO</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>controlli</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>Iscriviti</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Chiudi</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>tu@esempio.com</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(opzionale)</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Annulla</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>Iscriviti</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Chiudi</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Errore:</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>Converti in XML</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>Converti in JSON</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>Converti in ICC</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>Conversione in XML…</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>ID profilo</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Nome tag</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Offset</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Dimensione</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Riempimento</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Tipo</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Array di {type}</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>byte</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>Il profilo è valido</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Errore di convalida critico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Valido</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Avviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Errore</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Sconosciuto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Superato</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Non superato</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Attivato da</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Campo</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Valore attuale</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Richiesto: 0</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Atteso: {value}</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>Non valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Chiudi</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>rientro</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>ordina chiavi</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>